--- a/resources/report/60/95/einvoices_template/TID_111_VAT INVOICE.xlsx
+++ b/resources/report/60/95/einvoices_template/TID_111_VAT INVOICE.xlsx
@@ -667,7 +667,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="55" x14ac:knownFonts="1">
+  <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -963,13 +963,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
@@ -1001,14 +994,15 @@
       <family val="1"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color indexed="8"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1684,7 +1678,7 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1931,7 +1925,6 @@
     <xf numFmtId="0" fontId="30" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1950,19 +1943,19 @@
     <xf numFmtId="0" fontId="40" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="48" fillId="18" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="47" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="47" fillId="18" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1978,6 +1971,21 @@
     <xf numFmtId="0" fontId="30" fillId="18" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2104,9 +2112,6 @@
     <xf numFmtId="0" fontId="9" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2122,7 +2127,7 @@
     <xf numFmtId="0" fontId="27" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2134,18 +2139,13 @@
     <xf numFmtId="0" fontId="5" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="18" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -2519,22 +2519,22 @@
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
       <c r="E2" s="36"/>
-      <c r="F2" s="109" t="s">
+      <c r="F2" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
-      <c r="L2" s="109"/>
-      <c r="M2" s="109"/>
-      <c r="N2" s="104" t="s">
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="104"/>
-      <c r="P2" s="104"/>
-      <c r="Q2" s="104"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="108"/>
       <c r="R2" s="37"/>
       <c r="S2" s="11"/>
     </row>
@@ -2544,39 +2544,39 @@
       <c r="C3" s="39"/>
       <c r="D3" s="39"/>
       <c r="E3" s="39"/>
-      <c r="F3" s="110" t="s">
+      <c r="F3" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="105" t="s">
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="114"/>
+      <c r="K3" s="114"/>
+      <c r="L3" s="114"/>
+      <c r="M3" s="114"/>
+      <c r="N3" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="105"/>
-      <c r="P3" s="105"/>
-      <c r="Q3" s="105"/>
+      <c r="O3" s="109"/>
+      <c r="P3" s="109"/>
+      <c r="Q3" s="109"/>
       <c r="R3" s="40"/>
       <c r="S3" s="12"/>
     </row>
-    <row r="4" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="4.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="38"/>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
       <c r="D4" s="39"/>
       <c r="E4" s="39"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="146"/>
+      <c r="F4" s="149"/>
+      <c r="G4" s="149"/>
+      <c r="H4" s="149"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="149"/>
+      <c r="K4" s="149"/>
+      <c r="L4" s="149"/>
+      <c r="M4" s="149"/>
       <c r="N4" s="41"/>
       <c r="O4" s="41"/>
       <c r="P4" s="41"/>
@@ -2590,15 +2590,15 @@
       <c r="C5" s="39"/>
       <c r="D5" s="39"/>
       <c r="E5" s="39"/>
-      <c r="F5" s="108" t="s">
+      <c r="F5" s="112" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="108"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112"/>
       <c r="M5" s="41"/>
       <c r="N5" s="41"/>
       <c r="O5" s="41"/>
@@ -2632,20 +2632,20 @@
       <c r="A7" s="38"/>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
-      <c r="D7" s="106" t="s">
+      <c r="D7" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="111"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="111"/>
       <c r="P7" s="39"/>
       <c r="Q7" s="39"/>
       <c r="R7" s="39"/>
@@ -2682,19 +2682,19 @@
       <c r="E9" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="111"/>
-      <c r="G9" s="111"/>
-      <c r="H9" s="111"/>
-      <c r="I9" s="111"/>
-      <c r="J9" s="111"/>
-      <c r="K9" s="111"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="111"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="115"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="115"/>
+      <c r="N9" s="115"/>
+      <c r="O9" s="115"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="115"/>
+      <c r="R9" s="115"/>
       <c r="S9" s="14"/>
     </row>
     <row r="10" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2707,19 +2707,19 @@
       <c r="E10" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="112"/>
-      <c r="K10" s="112"/>
-      <c r="L10" s="112"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="112"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="112"/>
-      <c r="Q10" s="112"/>
-      <c r="R10" s="112"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="116"/>
+      <c r="L10" s="116"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="116"/>
+      <c r="O10" s="116"/>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
       <c r="S10" s="12"/>
     </row>
     <row r="11" spans="1:19" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -2732,19 +2732,19 @@
       <c r="E11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103"/>
-      <c r="L11" s="103"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="103"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="103"/>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="103"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107"/>
+      <c r="J11" s="107"/>
+      <c r="K11" s="107"/>
+      <c r="L11" s="107"/>
+      <c r="M11" s="107"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="107"/>
+      <c r="P11" s="107"/>
+      <c r="Q11" s="107"/>
+      <c r="R11" s="107"/>
       <c r="S11" s="12"/>
     </row>
     <row r="12" spans="1:19" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2757,11 +2757,11 @@
       <c r="E12" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="113"/>
-      <c r="I12" s="113"/>
-      <c r="J12" s="113"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="117"/>
+      <c r="J12" s="117"/>
       <c r="K12" s="43"/>
       <c r="L12" s="43"/>
       <c r="M12" s="43"/>
@@ -2782,19 +2782,19 @@
       <c r="E13" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="113"/>
-      <c r="K13" s="113"/>
-      <c r="L13" s="113"/>
-      <c r="M13" s="113"/>
-      <c r="N13" s="113"/>
-      <c r="O13" s="113"/>
-      <c r="P13" s="113"/>
-      <c r="Q13" s="113"/>
-      <c r="R13" s="113"/>
+      <c r="F13" s="158"/>
+      <c r="G13" s="158"/>
+      <c r="H13" s="158"/>
+      <c r="I13" s="158"/>
+      <c r="J13" s="158"/>
+      <c r="K13" s="158"/>
+      <c r="L13" s="158"/>
+      <c r="M13" s="158"/>
+      <c r="N13" s="158"/>
+      <c r="O13" s="158"/>
+      <c r="P13" s="158"/>
+      <c r="Q13" s="158"/>
+      <c r="R13" s="158"/>
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
@@ -2803,22 +2803,22 @@
       <c r="C14" s="39"/>
       <c r="D14" s="39"/>
       <c r="E14" s="39"/>
-      <c r="F14" s="145"/>
-      <c r="G14" s="145"/>
-      <c r="H14" s="145"/>
-      <c r="I14" s="145"/>
-      <c r="J14" s="145"/>
-      <c r="K14" s="145"/>
-      <c r="L14" s="145"/>
-      <c r="M14" s="145"/>
-      <c r="N14" s="145"/>
-      <c r="O14" s="145"/>
-      <c r="P14" s="145"/>
-      <c r="Q14" s="145"/>
-      <c r="R14" s="145"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="159"/>
+      <c r="H14" s="159"/>
+      <c r="I14" s="159"/>
+      <c r="J14" s="159"/>
+      <c r="K14" s="159"/>
+      <c r="L14" s="159"/>
+      <c r="M14" s="159"/>
+      <c r="N14" s="159"/>
+      <c r="O14" s="159"/>
+      <c r="P14" s="159"/>
+      <c r="Q14" s="159"/>
+      <c r="R14" s="159"/>
       <c r="S14" s="13"/>
     </row>
-    <row r="15" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="1.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="38"/>
       <c r="B15" s="48"/>
       <c r="C15" s="48"/>
@@ -3025,68 +3025,68 @@
     </row>
     <row r="24" spans="1:19" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
       <c r="A24" s="56"/>
-      <c r="B24" s="100" t="s">
+      <c r="B24" s="99" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="114" t="s">
+      <c r="C24" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="114"/>
-      <c r="E24" s="114"/>
-      <c r="F24" s="114"/>
-      <c r="G24" s="114"/>
-      <c r="H24" s="114"/>
-      <c r="I24" s="114"/>
-      <c r="J24" s="101" t="s">
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="K24" s="114" t="s">
+      <c r="K24" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="L24" s="114"/>
-      <c r="M24" s="114"/>
-      <c r="N24" s="114" t="s">
+      <c r="L24" s="118"/>
+      <c r="M24" s="118"/>
+      <c r="N24" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="114"/>
-      <c r="P24" s="114"/>
-      <c r="Q24" s="114" t="s">
+      <c r="O24" s="118"/>
+      <c r="P24" s="118"/>
+      <c r="Q24" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="R24" s="114"/>
+      <c r="R24" s="118"/>
       <c r="S24" s="16"/>
     </row>
     <row r="25" spans="1:19" s="4" customFormat="1" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="57"/>
-      <c r="B25" s="102" t="s">
+      <c r="B25" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="115" t="s">
+      <c r="C25" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="115"/>
-      <c r="E25" s="115"/>
-      <c r="F25" s="115"/>
-      <c r="G25" s="115"/>
-      <c r="H25" s="115"/>
-      <c r="I25" s="115"/>
-      <c r="J25" s="102" t="s">
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="119"/>
+      <c r="H25" s="119"/>
+      <c r="I25" s="119"/>
+      <c r="J25" s="101" t="s">
         <v>3</v>
       </c>
-      <c r="K25" s="115" t="s">
+      <c r="K25" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="115"/>
-      <c r="M25" s="115"/>
-      <c r="N25" s="115" t="s">
+      <c r="L25" s="119"/>
+      <c r="M25" s="119"/>
+      <c r="N25" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="O25" s="115"/>
-      <c r="P25" s="115"/>
-      <c r="Q25" s="115" t="s">
+      <c r="O25" s="119"/>
+      <c r="P25" s="119"/>
+      <c r="Q25" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="R25" s="115"/>
+      <c r="R25" s="119"/>
       <c r="S25" s="17"/>
     </row>
     <row r="26" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3094,244 +3094,244 @@
       <c r="B26" s="59">
         <v>1</v>
       </c>
-      <c r="C26" s="116">
+      <c r="C26" s="120">
         <v>2</v>
       </c>
-      <c r="D26" s="116"/>
-      <c r="E26" s="116"/>
-      <c r="F26" s="116"/>
-      <c r="G26" s="116"/>
-      <c r="H26" s="116"/>
-      <c r="I26" s="116"/>
+      <c r="D26" s="120"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="120"/>
+      <c r="H26" s="120"/>
+      <c r="I26" s="120"/>
       <c r="J26" s="59">
         <v>3</v>
       </c>
-      <c r="K26" s="116">
+      <c r="K26" s="120">
         <v>4</v>
       </c>
-      <c r="L26" s="116"/>
-      <c r="M26" s="116"/>
-      <c r="N26" s="116">
+      <c r="L26" s="120"/>
+      <c r="M26" s="120"/>
+      <c r="N26" s="120">
         <v>5</v>
       </c>
-      <c r="O26" s="116"/>
-      <c r="P26" s="116"/>
-      <c r="Q26" s="116" t="s">
+      <c r="O26" s="120"/>
+      <c r="P26" s="120"/>
+      <c r="Q26" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="R26" s="116"/>
+      <c r="R26" s="120"/>
       <c r="S26" s="18"/>
     </row>
     <row r="27" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="60"/>
       <c r="B27" s="61"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="118"/>
-      <c r="G27" s="118"/>
-      <c r="H27" s="118"/>
-      <c r="I27" s="119"/>
+      <c r="C27" s="121"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="122"/>
+      <c r="G27" s="122"/>
+      <c r="H27" s="122"/>
+      <c r="I27" s="123"/>
       <c r="J27" s="62"/>
-      <c r="K27" s="124"/>
-      <c r="L27" s="125"/>
+      <c r="K27" s="128"/>
+      <c r="L27" s="129"/>
       <c r="M27" s="63"/>
-      <c r="N27" s="120"/>
-      <c r="O27" s="121"/>
+      <c r="N27" s="124"/>
+      <c r="O27" s="125"/>
       <c r="P27" s="63"/>
-      <c r="Q27" s="122"/>
-      <c r="R27" s="123"/>
+      <c r="Q27" s="126"/>
+      <c r="R27" s="127"/>
       <c r="S27" s="30"/>
     </row>
     <row r="28" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="60"/>
       <c r="B28" s="64"/>
-      <c r="C28" s="126" t="s">
+      <c r="C28" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="127"/>
-      <c r="E28" s="127"/>
-      <c r="F28" s="127"/>
-      <c r="G28" s="127"/>
-      <c r="H28" s="127"/>
-      <c r="I28" s="128"/>
+      <c r="D28" s="131"/>
+      <c r="E28" s="131"/>
+      <c r="F28" s="131"/>
+      <c r="G28" s="131"/>
+      <c r="H28" s="131"/>
+      <c r="I28" s="132"/>
       <c r="J28" s="62"/>
-      <c r="K28" s="120"/>
-      <c r="L28" s="121"/>
+      <c r="K28" s="124"/>
+      <c r="L28" s="125"/>
       <c r="M28" s="63"/>
-      <c r="N28" s="120"/>
-      <c r="O28" s="121"/>
+      <c r="N28" s="124"/>
+      <c r="O28" s="125"/>
       <c r="P28" s="63"/>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="123"/>
+      <c r="Q28" s="126"/>
+      <c r="R28" s="127"/>
       <c r="S28" s="30"/>
     </row>
     <row r="29" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="60"/>
       <c r="B29" s="64"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="118"/>
-      <c r="G29" s="118"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="119"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="122"/>
+      <c r="G29" s="122"/>
+      <c r="H29" s="122"/>
+      <c r="I29" s="123"/>
       <c r="J29" s="62"/>
-      <c r="K29" s="120"/>
-      <c r="L29" s="121"/>
+      <c r="K29" s="124"/>
+      <c r="L29" s="125"/>
       <c r="M29" s="63"/>
-      <c r="N29" s="120"/>
-      <c r="O29" s="121"/>
+      <c r="N29" s="124"/>
+      <c r="O29" s="125"/>
       <c r="P29" s="63"/>
-      <c r="Q29" s="122"/>
-      <c r="R29" s="123"/>
+      <c r="Q29" s="126"/>
+      <c r="R29" s="127"/>
       <c r="S29" s="30"/>
     </row>
     <row r="30" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="60"/>
       <c r="B30" s="64"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="118"/>
-      <c r="G30" s="118"/>
-      <c r="H30" s="118"/>
-      <c r="I30" s="119"/>
+      <c r="C30" s="121"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="122"/>
+      <c r="F30" s="122"/>
+      <c r="G30" s="122"/>
+      <c r="H30" s="122"/>
+      <c r="I30" s="123"/>
       <c r="J30" s="62"/>
-      <c r="K30" s="120"/>
-      <c r="L30" s="121"/>
+      <c r="K30" s="124"/>
+      <c r="L30" s="125"/>
       <c r="M30" s="63"/>
-      <c r="N30" s="120"/>
-      <c r="O30" s="121"/>
+      <c r="N30" s="124"/>
+      <c r="O30" s="125"/>
       <c r="P30" s="63"/>
-      <c r="Q30" s="122"/>
-      <c r="R30" s="123"/>
+      <c r="Q30" s="126"/>
+      <c r="R30" s="127"/>
       <c r="S30" s="30"/>
     </row>
     <row r="31" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="60"/>
       <c r="B31" s="64"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="118"/>
-      <c r="G31" s="118"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="119"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="122"/>
+      <c r="E31" s="122"/>
+      <c r="F31" s="122"/>
+      <c r="G31" s="122"/>
+      <c r="H31" s="122"/>
+      <c r="I31" s="123"/>
       <c r="J31" s="62"/>
-      <c r="K31" s="120"/>
-      <c r="L31" s="121"/>
+      <c r="K31" s="124"/>
+      <c r="L31" s="125"/>
       <c r="M31" s="63"/>
-      <c r="N31" s="120"/>
-      <c r="O31" s="121"/>
+      <c r="N31" s="124"/>
+      <c r="O31" s="125"/>
       <c r="P31" s="63"/>
-      <c r="Q31" s="122"/>
-      <c r="R31" s="123"/>
+      <c r="Q31" s="126"/>
+      <c r="R31" s="127"/>
       <c r="S31" s="30"/>
     </row>
     <row r="32" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60"/>
       <c r="B32" s="64"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="118"/>
-      <c r="G32" s="118"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="119"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="122"/>
+      <c r="G32" s="122"/>
+      <c r="H32" s="122"/>
+      <c r="I32" s="123"/>
       <c r="J32" s="62"/>
-      <c r="K32" s="120"/>
-      <c r="L32" s="121"/>
+      <c r="K32" s="124"/>
+      <c r="L32" s="125"/>
       <c r="M32" s="63"/>
-      <c r="N32" s="120"/>
-      <c r="O32" s="121"/>
+      <c r="N32" s="124"/>
+      <c r="O32" s="125"/>
       <c r="P32" s="63"/>
-      <c r="Q32" s="122"/>
-      <c r="R32" s="123"/>
+      <c r="Q32" s="126"/>
+      <c r="R32" s="127"/>
       <c r="S32" s="30"/>
     </row>
     <row r="33" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="60"/>
       <c r="B33" s="64"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="118"/>
-      <c r="G33" s="118"/>
-      <c r="H33" s="118"/>
-      <c r="I33" s="119"/>
+      <c r="C33" s="121"/>
+      <c r="D33" s="122"/>
+      <c r="E33" s="122"/>
+      <c r="F33" s="122"/>
+      <c r="G33" s="122"/>
+      <c r="H33" s="122"/>
+      <c r="I33" s="123"/>
       <c r="J33" s="65"/>
-      <c r="K33" s="120"/>
-      <c r="L33" s="121"/>
+      <c r="K33" s="124"/>
+      <c r="L33" s="125"/>
       <c r="M33" s="63"/>
-      <c r="N33" s="120"/>
-      <c r="O33" s="121"/>
+      <c r="N33" s="124"/>
+      <c r="O33" s="125"/>
       <c r="P33" s="63"/>
-      <c r="Q33" s="122"/>
-      <c r="R33" s="123"/>
+      <c r="Q33" s="126"/>
+      <c r="R33" s="127"/>
       <c r="S33" s="30"/>
     </row>
     <row r="34" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="66"/>
       <c r="B34" s="67"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="118"/>
-      <c r="G34" s="118"/>
-      <c r="H34" s="118"/>
-      <c r="I34" s="119"/>
+      <c r="C34" s="121"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="122"/>
+      <c r="F34" s="122"/>
+      <c r="G34" s="122"/>
+      <c r="H34" s="122"/>
+      <c r="I34" s="123"/>
       <c r="J34" s="65"/>
-      <c r="K34" s="120"/>
-      <c r="L34" s="121"/>
+      <c r="K34" s="124"/>
+      <c r="L34" s="125"/>
       <c r="M34" s="63"/>
-      <c r="N34" s="120"/>
-      <c r="O34" s="121"/>
+      <c r="N34" s="124"/>
+      <c r="O34" s="125"/>
       <c r="P34" s="63"/>
-      <c r="Q34" s="122"/>
-      <c r="R34" s="123"/>
+      <c r="Q34" s="126"/>
+      <c r="R34" s="127"/>
       <c r="S34" s="30"/>
     </row>
     <row r="35" spans="1:19" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="60"/>
       <c r="B35" s="64"/>
-      <c r="C35" s="117"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="118"/>
-      <c r="G35" s="118"/>
-      <c r="H35" s="118"/>
-      <c r="I35" s="119"/>
+      <c r="C35" s="121"/>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="123"/>
       <c r="J35" s="65"/>
-      <c r="K35" s="120"/>
-      <c r="L35" s="121"/>
+      <c r="K35" s="124"/>
+      <c r="L35" s="125"/>
       <c r="M35" s="63"/>
-      <c r="N35" s="120"/>
-      <c r="O35" s="121"/>
+      <c r="N35" s="124"/>
+      <c r="O35" s="125"/>
       <c r="P35" s="63"/>
-      <c r="Q35" s="122"/>
-      <c r="R35" s="123"/>
+      <c r="Q35" s="126"/>
+      <c r="R35" s="127"/>
       <c r="S35" s="30"/>
     </row>
     <row r="36" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="60"/>
       <c r="B36" s="61"/>
-      <c r="C36" s="142"/>
-      <c r="D36" s="143"/>
-      <c r="E36" s="143"/>
-      <c r="F36" s="143"/>
-      <c r="G36" s="143"/>
-      <c r="H36" s="143"/>
-      <c r="I36" s="144"/>
+      <c r="C36" s="146"/>
+      <c r="D36" s="147"/>
+      <c r="E36" s="147"/>
+      <c r="F36" s="147"/>
+      <c r="G36" s="147"/>
+      <c r="H36" s="147"/>
+      <c r="I36" s="148"/>
       <c r="J36" s="68"/>
-      <c r="K36" s="140"/>
-      <c r="L36" s="141"/>
+      <c r="K36" s="144"/>
+      <c r="L36" s="145"/>
       <c r="M36" s="69"/>
-      <c r="N36" s="130"/>
-      <c r="O36" s="131"/>
+      <c r="N36" s="134"/>
+      <c r="O36" s="135"/>
       <c r="P36" s="69"/>
-      <c r="Q36" s="130"/>
-      <c r="R36" s="132"/>
+      <c r="Q36" s="134"/>
+      <c r="R36" s="136"/>
       <c r="S36" s="31"/>
     </row>
     <row r="37" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3344,42 +3344,42 @@
       <c r="G37" s="71"/>
       <c r="H37" s="71"/>
       <c r="I37" s="71"/>
-      <c r="J37" s="133" t="s">
+      <c r="J37" s="137" t="s">
         <v>44</v>
       </c>
-      <c r="K37" s="133"/>
-      <c r="L37" s="133"/>
-      <c r="M37" s="133"/>
-      <c r="N37" s="133"/>
-      <c r="O37" s="133"/>
-      <c r="P37" s="134"/>
-      <c r="Q37" s="135"/>
-      <c r="R37" s="136"/>
+      <c r="K37" s="137"/>
+      <c r="L37" s="137"/>
+      <c r="M37" s="137"/>
+      <c r="N37" s="137"/>
+      <c r="O37" s="137"/>
+      <c r="P37" s="138"/>
+      <c r="Q37" s="139"/>
+      <c r="R37" s="140"/>
       <c r="S37" s="32"/>
     </row>
     <row r="38" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="60"/>
-      <c r="B38" s="138" t="s">
+      <c r="B38" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="139"/>
-      <c r="D38" s="139"/>
-      <c r="E38" s="139"/>
-      <c r="F38" s="139"/>
+      <c r="C38" s="143"/>
+      <c r="D38" s="143"/>
+      <c r="E38" s="143"/>
+      <c r="F38" s="143"/>
       <c r="G38" s="72"/>
       <c r="H38" s="73"/>
       <c r="I38" s="72"/>
-      <c r="J38" s="133" t="s">
+      <c r="J38" s="137" t="s">
         <v>45</v>
       </c>
-      <c r="K38" s="133"/>
-      <c r="L38" s="133"/>
-      <c r="M38" s="133"/>
-      <c r="N38" s="133"/>
-      <c r="O38" s="133"/>
-      <c r="P38" s="134"/>
-      <c r="Q38" s="135"/>
-      <c r="R38" s="136"/>
+      <c r="K38" s="137"/>
+      <c r="L38" s="137"/>
+      <c r="M38" s="137"/>
+      <c r="N38" s="137"/>
+      <c r="O38" s="137"/>
+      <c r="P38" s="138"/>
+      <c r="Q38" s="139"/>
+      <c r="R38" s="140"/>
       <c r="S38" s="32"/>
     </row>
     <row r="39" spans="1:19" s="6" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3392,40 +3392,40 @@
       <c r="G39" s="72"/>
       <c r="H39" s="72"/>
       <c r="I39" s="72"/>
-      <c r="J39" s="133" t="s">
+      <c r="J39" s="137" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="133"/>
-      <c r="L39" s="133"/>
-      <c r="M39" s="133"/>
-      <c r="N39" s="133"/>
-      <c r="O39" s="133"/>
-      <c r="P39" s="134"/>
-      <c r="Q39" s="135"/>
-      <c r="R39" s="136"/>
+      <c r="K39" s="137"/>
+      <c r="L39" s="137"/>
+      <c r="M39" s="137"/>
+      <c r="N39" s="137"/>
+      <c r="O39" s="137"/>
+      <c r="P39" s="138"/>
+      <c r="Q39" s="139"/>
+      <c r="R39" s="140"/>
       <c r="S39" s="32"/>
     </row>
     <row r="40" spans="1:19" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="56"/>
-      <c r="B40" s="152" t="s">
+      <c r="B40" s="155" t="s">
         <v>23</v>
       </c>
-      <c r="C40" s="153"/>
-      <c r="D40" s="153"/>
-      <c r="E40" s="153"/>
-      <c r="F40" s="153"/>
-      <c r="G40" s="153"/>
-      <c r="H40" s="153"/>
-      <c r="I40" s="153"/>
-      <c r="J40" s="153"/>
-      <c r="K40" s="153"/>
-      <c r="L40" s="153"/>
-      <c r="M40" s="153"/>
-      <c r="N40" s="153"/>
-      <c r="O40" s="153"/>
-      <c r="P40" s="153"/>
-      <c r="Q40" s="153"/>
-      <c r="R40" s="154"/>
+      <c r="C40" s="156"/>
+      <c r="D40" s="156"/>
+      <c r="E40" s="156"/>
+      <c r="F40" s="156"/>
+      <c r="G40" s="156"/>
+      <c r="H40" s="156"/>
+      <c r="I40" s="156"/>
+      <c r="J40" s="156"/>
+      <c r="K40" s="156"/>
+      <c r="L40" s="156"/>
+      <c r="M40" s="156"/>
+      <c r="N40" s="156"/>
+      <c r="O40" s="156"/>
+      <c r="P40" s="156"/>
+      <c r="Q40" s="156"/>
+      <c r="R40" s="157"/>
       <c r="S40" s="19"/>
     </row>
     <row r="41" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -3452,79 +3452,79 @@
     <row r="42" spans="1:19" s="7" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="79"/>
       <c r="B42" s="80"/>
-      <c r="C42" s="149" t="s">
+      <c r="C42" s="152" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="149"/>
-      <c r="E42" s="149"/>
-      <c r="F42" s="149"/>
-      <c r="G42" s="149"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="149"/>
-      <c r="J42" s="149"/>
-      <c r="K42" s="149"/>
-      <c r="L42" s="149" t="s">
+      <c r="D42" s="152"/>
+      <c r="E42" s="152"/>
+      <c r="F42" s="152"/>
+      <c r="G42" s="152"/>
+      <c r="H42" s="152"/>
+      <c r="I42" s="152"/>
+      <c r="J42" s="152"/>
+      <c r="K42" s="152"/>
+      <c r="L42" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="M42" s="149"/>
-      <c r="N42" s="149"/>
-      <c r="O42" s="149"/>
-      <c r="P42" s="149"/>
-      <c r="Q42" s="149"/>
-      <c r="R42" s="149"/>
+      <c r="M42" s="152"/>
+      <c r="N42" s="152"/>
+      <c r="O42" s="152"/>
+      <c r="P42" s="152"/>
+      <c r="Q42" s="152"/>
+      <c r="R42" s="152"/>
       <c r="S42" s="21"/>
     </row>
     <row r="43" spans="1:19" s="8" customFormat="1" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="81"/>
       <c r="B43" s="82"/>
-      <c r="C43" s="137" t="s">
+      <c r="C43" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="137"/>
-      <c r="E43" s="137"/>
-      <c r="F43" s="137"/>
-      <c r="G43" s="137"/>
-      <c r="H43" s="137"/>
-      <c r="I43" s="137"/>
-      <c r="J43" s="137"/>
-      <c r="K43" s="137"/>
-      <c r="L43" s="137" t="s">
+      <c r="D43" s="141"/>
+      <c r="E43" s="141"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="141"/>
+      <c r="H43" s="141"/>
+      <c r="I43" s="141"/>
+      <c r="J43" s="141"/>
+      <c r="K43" s="141"/>
+      <c r="L43" s="141" t="s">
         <v>9</v>
       </c>
-      <c r="M43" s="137"/>
-      <c r="N43" s="137"/>
-      <c r="O43" s="137"/>
-      <c r="P43" s="137"/>
-      <c r="Q43" s="137"/>
-      <c r="R43" s="137"/>
+      <c r="M43" s="141"/>
+      <c r="N43" s="141"/>
+      <c r="O43" s="141"/>
+      <c r="P43" s="141"/>
+      <c r="Q43" s="141"/>
+      <c r="R43" s="141"/>
       <c r="S43" s="22"/>
     </row>
     <row r="44" spans="1:19" s="9" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="57"/>
       <c r="B44" s="83"/>
-      <c r="C44" s="129" t="s">
+      <c r="C44" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="D44" s="129"/>
-      <c r="E44" s="129"/>
-      <c r="F44" s="129"/>
-      <c r="G44" s="129"/>
-      <c r="H44" s="129"/>
-      <c r="I44" s="129"/>
-      <c r="J44" s="129"/>
-      <c r="K44" s="129"/>
-      <c r="L44" s="129" t="s">
+      <c r="D44" s="133"/>
+      <c r="E44" s="133"/>
+      <c r="F44" s="133"/>
+      <c r="G44" s="133"/>
+      <c r="H44" s="133"/>
+      <c r="I44" s="133"/>
+      <c r="J44" s="133"/>
+      <c r="K44" s="133"/>
+      <c r="L44" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="M44" s="129"/>
-      <c r="N44" s="129"/>
-      <c r="O44" s="129"/>
-      <c r="P44" s="129"/>
-      <c r="Q44" s="129"/>
-      <c r="R44" s="129"/>
+      <c r="M44" s="133"/>
+      <c r="N44" s="133"/>
+      <c r="O44" s="133"/>
+      <c r="P44" s="133"/>
+      <c r="Q44" s="133"/>
+      <c r="R44" s="133"/>
       <c r="S44" s="23"/>
     </row>
-    <row r="45" spans="1:19" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="4.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="38"/>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -3557,43 +3557,43 @@
       <c r="I46" s="43"/>
       <c r="J46" s="43"/>
       <c r="K46" s="39"/>
-      <c r="L46" s="84" t="s">
+      <c r="L46" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="M46" s="85"/>
-      <c r="N46" s="85"/>
-      <c r="O46" s="85"/>
-      <c r="P46" s="86"/>
-      <c r="Q46" s="86"/>
-      <c r="R46" s="87"/>
+      <c r="M46" s="84"/>
+      <c r="N46" s="84"/>
+      <c r="O46" s="84"/>
+      <c r="P46" s="85"/>
+      <c r="Q46" s="85"/>
+      <c r="R46" s="86"/>
       <c r="S46" s="25"/>
     </row>
-    <row r="47" spans="1:19" s="10" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A47" s="88"/>
-      <c r="B47" s="89"/>
-      <c r="C47" s="89"/>
-      <c r="D47" s="89"/>
-      <c r="E47" s="89"/>
-      <c r="F47" s="90"/>
-      <c r="G47" s="90"/>
-      <c r="H47" s="90"/>
-      <c r="I47" s="90"/>
-      <c r="J47" s="90"/>
-      <c r="K47" s="89"/>
-      <c r="L47" s="155" t="s">
+    <row r="47" spans="1:19" s="10" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="87"/>
+      <c r="B47" s="88"/>
+      <c r="C47" s="88"/>
+      <c r="D47" s="88"/>
+      <c r="E47" s="88"/>
+      <c r="F47" s="89"/>
+      <c r="G47" s="89"/>
+      <c r="H47" s="89"/>
+      <c r="I47" s="89"/>
+      <c r="J47" s="89"/>
+      <c r="K47" s="88"/>
+      <c r="L47" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="M47" s="156"/>
-      <c r="N47" s="156"/>
-      <c r="O47" s="156"/>
-      <c r="P47" s="156"/>
-      <c r="Q47" s="156"/>
-      <c r="R47" s="157"/>
+      <c r="M47" s="103"/>
+      <c r="N47" s="103"/>
+      <c r="O47" s="105"/>
+      <c r="P47" s="105"/>
+      <c r="Q47" s="105"/>
+      <c r="R47" s="106"/>
       <c r="S47" s="26"/>
     </row>
     <row r="48" spans="1:19" ht="13.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="38"/>
-      <c r="B48" s="91"/>
+      <c r="B48" s="90"/>
       <c r="C48" s="39"/>
       <c r="D48" s="39"/>
       <c r="E48" s="39"/>
@@ -3603,23 +3603,23 @@
       <c r="I48" s="43"/>
       <c r="J48" s="43"/>
       <c r="K48" s="39"/>
-      <c r="L48" s="158" t="s">
+      <c r="L48" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="M48" s="92"/>
-      <c r="N48" s="93"/>
-      <c r="O48" s="93"/>
-      <c r="P48" s="93"/>
-      <c r="Q48" s="93"/>
-      <c r="R48" s="94"/>
+      <c r="M48" s="91"/>
+      <c r="N48" s="92"/>
+      <c r="O48" s="92"/>
+      <c r="P48" s="92"/>
+      <c r="Q48" s="92"/>
+      <c r="R48" s="93"/>
       <c r="S48" s="27"/>
     </row>
-    <row r="49" spans="1:19" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="38"/>
-      <c r="B49" s="95"/>
-      <c r="C49" s="96"/>
-      <c r="D49" s="96"/>
-      <c r="E49" s="96"/>
+      <c r="B49" s="94"/>
+      <c r="C49" s="95"/>
+      <c r="D49" s="95"/>
+      <c r="E49" s="95"/>
       <c r="F49" s="43"/>
       <c r="G49" s="43"/>
       <c r="H49" s="43"/>
@@ -3637,19 +3637,19 @@
     </row>
     <row r="50" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="38"/>
-      <c r="B50" s="97" t="s">
+      <c r="B50" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="98"/>
-      <c r="D50" s="98"/>
-      <c r="E50" s="98"/>
-      <c r="F50" s="98"/>
-      <c r="G50" s="151"/>
-      <c r="H50" s="151"/>
-      <c r="I50" s="151"/>
-      <c r="J50" s="151"/>
+      <c r="C50" s="97"/>
+      <c r="D50" s="97"/>
+      <c r="E50" s="97"/>
+      <c r="F50" s="97"/>
+      <c r="G50" s="154"/>
+      <c r="H50" s="154"/>
+      <c r="I50" s="154"/>
+      <c r="J50" s="154"/>
       <c r="K50" s="39"/>
-      <c r="L50" s="95"/>
+      <c r="L50" s="94"/>
       <c r="M50" s="43"/>
       <c r="N50" s="43"/>
       <c r="O50" s="43"/>
@@ -3660,19 +3660,19 @@
     </row>
     <row r="51" spans="1:19" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="38"/>
-      <c r="B51" s="150" t="s">
+      <c r="B51" s="153" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="150"/>
-      <c r="D51" s="150"/>
-      <c r="E51" s="150"/>
-      <c r="F51" s="150"/>
-      <c r="G51" s="150"/>
-      <c r="H51" s="150"/>
-      <c r="I51" s="150"/>
-      <c r="J51" s="150"/>
-      <c r="K51" s="150"/>
-      <c r="L51" s="95"/>
+      <c r="C51" s="153"/>
+      <c r="D51" s="153"/>
+      <c r="E51" s="153"/>
+      <c r="F51" s="153"/>
+      <c r="G51" s="153"/>
+      <c r="H51" s="153"/>
+      <c r="I51" s="153"/>
+      <c r="J51" s="153"/>
+      <c r="K51" s="153"/>
+      <c r="L51" s="94"/>
       <c r="M51" s="43"/>
       <c r="N51" s="43"/>
       <c r="O51" s="43"/>
@@ -3682,61 +3682,59 @@
       <c r="S51" s="24"/>
     </row>
     <row r="52" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="99"/>
-      <c r="B52" s="147" t="s">
+      <c r="A52" s="98"/>
+      <c r="B52" s="150" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="147"/>
-      <c r="D52" s="147"/>
-      <c r="E52" s="147"/>
-      <c r="F52" s="147"/>
-      <c r="G52" s="147"/>
-      <c r="H52" s="147"/>
-      <c r="I52" s="147"/>
-      <c r="J52" s="147"/>
-      <c r="K52" s="147"/>
-      <c r="L52" s="147"/>
-      <c r="M52" s="147"/>
-      <c r="N52" s="147"/>
-      <c r="O52" s="147"/>
-      <c r="P52" s="147"/>
-      <c r="Q52" s="147"/>
-      <c r="R52" s="147"/>
+      <c r="C52" s="150"/>
+      <c r="D52" s="150"/>
+      <c r="E52" s="150"/>
+      <c r="F52" s="150"/>
+      <c r="G52" s="150"/>
+      <c r="H52" s="150"/>
+      <c r="I52" s="150"/>
+      <c r="J52" s="150"/>
+      <c r="K52" s="150"/>
+      <c r="L52" s="150"/>
+      <c r="M52" s="150"/>
+      <c r="N52" s="150"/>
+      <c r="O52" s="150"/>
+      <c r="P52" s="150"/>
+      <c r="Q52" s="150"/>
+      <c r="R52" s="150"/>
       <c r="S52" s="28"/>
     </row>
     <row r="53" spans="1:19" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="39"/>
-      <c r="B53" s="148" t="s">
+      <c r="B53" s="151" t="s">
         <v>34</v>
       </c>
-      <c r="C53" s="148"/>
-      <c r="D53" s="148"/>
-      <c r="E53" s="148"/>
-      <c r="F53" s="148"/>
-      <c r="G53" s="148"/>
-      <c r="H53" s="148"/>
-      <c r="I53" s="148"/>
-      <c r="J53" s="148"/>
-      <c r="K53" s="148"/>
-      <c r="L53" s="148"/>
-      <c r="M53" s="148"/>
-      <c r="N53" s="148"/>
-      <c r="O53" s="148"/>
-      <c r="P53" s="148"/>
-      <c r="Q53" s="148"/>
-      <c r="R53" s="148"/>
+      <c r="C53" s="151"/>
+      <c r="D53" s="151"/>
+      <c r="E53" s="151"/>
+      <c r="F53" s="151"/>
+      <c r="G53" s="151"/>
+      <c r="H53" s="151"/>
+      <c r="I53" s="151"/>
+      <c r="J53" s="151"/>
+      <c r="K53" s="151"/>
+      <c r="L53" s="151"/>
+      <c r="M53" s="151"/>
+      <c r="N53" s="151"/>
+      <c r="O53" s="151"/>
+      <c r="P53" s="151"/>
+      <c r="Q53" s="151"/>
+      <c r="R53" s="151"/>
       <c r="S53" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="90">
-    <mergeCell ref="I14:R14"/>
     <mergeCell ref="F4:M4"/>
     <mergeCell ref="B52:R52"/>
     <mergeCell ref="B53:R53"/>
     <mergeCell ref="L42:R42"/>
     <mergeCell ref="L43:R43"/>
     <mergeCell ref="L44:R44"/>
-    <mergeCell ref="L47:R47"/>
     <mergeCell ref="B51:K51"/>
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="Q39:R39"/>
@@ -3764,6 +3762,11 @@
     <mergeCell ref="N35:O35"/>
     <mergeCell ref="C34:I34"/>
     <mergeCell ref="K33:L33"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="Q34:R34"/>
     <mergeCell ref="C30:I30"/>
     <mergeCell ref="Q30:R30"/>
     <mergeCell ref="C31:I31"/>
@@ -3776,11 +3779,6 @@
     <mergeCell ref="N31:O31"/>
     <mergeCell ref="N32:O32"/>
     <mergeCell ref="K30:L30"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="Q34:R34"/>
     <mergeCell ref="C29:I29"/>
     <mergeCell ref="N29:O29"/>
     <mergeCell ref="Q29:R29"/>
@@ -3793,22 +3791,19 @@
     <mergeCell ref="Q27:R27"/>
     <mergeCell ref="K28:L28"/>
     <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="K25:M25"/>
-    <mergeCell ref="N25:P25"/>
     <mergeCell ref="C26:I26"/>
     <mergeCell ref="K26:M26"/>
     <mergeCell ref="N26:P26"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="I13:R13"/>
     <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:R14"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="K25:M25"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="O47:R47"/>
     <mergeCell ref="F11:R11"/>
     <mergeCell ref="N2:Q2"/>
     <mergeCell ref="N3:Q3"/>
@@ -3819,6 +3814,11 @@
     <mergeCell ref="F3:M3"/>
     <mergeCell ref="F9:R9"/>
     <mergeCell ref="F10:R10"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="C24:I24"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
